--- a/B911306_송범규_requirement_list.xlsx
+++ b/B911306_송범규_requirement_list.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BK_\Documents\GitHub\SW_engineering_HW2\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{357BFABE-87EA-433D-8FCD-53080DCF3FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="jt2MnJ0NaIcGTH/oegSRMYGu/h/9+cv7oUBjbyIMHqE="/>
@@ -39,9 +48,6 @@
     <t>Use Case</t>
   </si>
   <si>
-    <t>사용자는 ID, 비밀번호, 전화번호를 입력하여 회원가입 가능</t>
-  </si>
-  <si>
     <t>회원가입</t>
   </si>
   <si>
@@ -79,46 +85,71 @@
   </si>
   <si>
     <t>시스템 종료</t>
+  </si>
+  <si>
+    <t>회원은 ID, 비밀번호, 전화번호를 입력하여 회원가입 가능</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
-    <font/>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -126,23 +157,32 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="5">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -152,6 +192,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -166,76 +207,83 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -425,213 +473,214 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:F1000"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="3" width="7.63"/>
-    <col customWidth="1" min="4" max="4" width="4.13"/>
-    <col customWidth="1" min="5" max="5" width="40.5"/>
-    <col customWidth="1" min="6" max="6" width="22.25"/>
-    <col customWidth="1" min="7" max="26" width="7.63"/>
+    <col min="1" max="2" width="7.5703125" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" customWidth="1"/>
+    <col min="4" max="4" width="4.140625" customWidth="1"/>
+    <col min="5" max="5" width="61.85546875" customWidth="1"/>
+    <col min="6" max="6" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="26" width="7.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.0" customHeight="1">
+    <row r="1" spans="2:6" ht="15" customHeight="1">
       <c r="C1" s="1"/>
     </row>
-    <row r="2" ht="16.5" customHeight="1">
+    <row r="2" spans="2:6" ht="16.5" customHeight="1">
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" ht="16.5" customHeight="1">
-      <c r="C3" s="3" t="s">
+    <row r="3" spans="2:6" ht="16.5" customHeight="1">
+      <c r="C3" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="5">
-        <v>15570.0</v>
-      </c>
-    </row>
-    <row r="4" ht="16.5" customHeight="1">
-      <c r="C4" s="3" t="s">
+      <c r="D3" s="11"/>
+      <c r="E3" s="3">
+        <v>15570</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="16.5" customHeight="1">
+      <c r="C4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="5" t="s">
+      <c r="D4" s="11"/>
+      <c r="E4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1">
+    <row r="5" spans="2:6" ht="16.5" customHeight="1">
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
-      <c r="E5" s="6"/>
-    </row>
-    <row r="6" ht="16.5" customHeight="1">
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="2:6" ht="16.5" customHeight="1">
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="6"/>
-    </row>
-    <row r="7" ht="16.5" customHeight="1"/>
-    <row r="8" ht="16.5" customHeight="1">
-      <c r="B8" s="7" t="s">
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="2:6" ht="16.5" customHeight="1"/>
+    <row r="8" spans="2:6" ht="16.5" customHeight="1">
+      <c r="B8" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="9" t="s">
+      <c r="C8" s="13"/>
+      <c r="D8" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1">
-      <c r="D9" s="10">
-        <v>1.0</v>
-      </c>
-      <c r="E9" s="11" t="s">
+    <row r="9" spans="2:6">
+      <c r="D9" s="6">
+        <v>1</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="10" t="s">
+    </row>
+    <row r="10" spans="2:6" ht="16.5" customHeight="1">
+      <c r="D10" s="6">
+        <v>2</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" ht="16.5" customHeight="1">
-      <c r="D10" s="10">
-        <v>2.0</v>
-      </c>
-      <c r="E10" s="11" t="s">
+      <c r="F10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="10" t="s">
+    </row>
+    <row r="11" spans="2:6" ht="16.5" customHeight="1">
+      <c r="D11" s="6">
+        <v>3</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" ht="16.5" customHeight="1">
-      <c r="D11" s="10">
-        <v>3.0</v>
-      </c>
-      <c r="E11" s="11" t="s">
+      <c r="F11" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="10" t="s">
+    </row>
+    <row r="12" spans="2:6">
+      <c r="D12" s="6">
+        <v>4</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" ht="16.5" customHeight="1">
-      <c r="D12" s="10">
-        <v>4.0</v>
-      </c>
-      <c r="E12" s="10" t="s">
+      <c r="F12" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="10" t="s">
+    </row>
+    <row r="13" spans="2:6">
+      <c r="D13" s="6">
+        <v>5</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="13" ht="16.5" customHeight="1">
-      <c r="D13" s="10">
-        <v>5.0</v>
-      </c>
-      <c r="E13" s="12" t="s">
+      <c r="F13" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="12" t="s">
+    </row>
+    <row r="14" spans="2:6">
+      <c r="D14" s="6">
+        <v>6</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" ht="16.5" customHeight="1">
-      <c r="D14" s="10">
-        <v>6.0</v>
-      </c>
-      <c r="E14" s="10" t="s">
+      <c r="F14" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="10" t="s">
+    </row>
+    <row r="15" spans="2:6">
+      <c r="D15" s="6">
+        <v>7</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="15" ht="16.5" customHeight="1">
-      <c r="D15" s="11">
-        <v>7.0</v>
-      </c>
-      <c r="E15" s="11" t="s">
+      <c r="F15" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" customHeight="1"/>
-    <row r="17" ht="16.5" customHeight="1">
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-    </row>
-    <row r="18" ht="16.5" customHeight="1">
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-    </row>
-    <row r="19" ht="16.5" customHeight="1">
-      <c r="D19" s="13"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-    </row>
-    <row r="20" ht="16.5" customHeight="1">
-      <c r="D20" s="13"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-    </row>
-    <row r="21" ht="16.5" customHeight="1">
+    </row>
+    <row r="16" spans="2:6" ht="16.5" customHeight="1"/>
+    <row r="17" spans="4:6" ht="16.5" customHeight="1">
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+    </row>
+    <row r="18" spans="4:6" ht="16.5" customHeight="1">
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+    </row>
+    <row r="19" spans="4:6" ht="16.5" customHeight="1">
+      <c r="D19" s="8"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="4:6" ht="16.5" customHeight="1">
+      <c r="D20" s="8"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" spans="4:6" ht="16.5" customHeight="1">
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" ht="16.5" customHeight="1">
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-    </row>
-    <row r="23" ht="16.5" customHeight="1">
+    <row r="22" spans="4:6" ht="16.5" customHeight="1">
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+    </row>
+    <row r="23" spans="4:6" ht="16.5" customHeight="1">
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" ht="16.5" customHeight="1">
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-    </row>
-    <row r="25" ht="16.5" customHeight="1">
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-    </row>
-    <row r="26" ht="16.5" customHeight="1">
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-    </row>
-    <row r="27" ht="16.5" customHeight="1">
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-    </row>
-    <row r="28" ht="16.5" customHeight="1"/>
-    <row r="29" ht="16.5" customHeight="1"/>
-    <row r="30" ht="16.5" customHeight="1"/>
-    <row r="31" ht="16.5" customHeight="1"/>
-    <row r="32" ht="16.5" customHeight="1"/>
+    <row r="24" spans="4:6" ht="16.5" customHeight="1">
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+    </row>
+    <row r="25" spans="4:6" ht="16.5" customHeight="1">
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+    </row>
+    <row r="26" spans="4:6" ht="16.5" customHeight="1">
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+    </row>
+    <row r="27" spans="4:6" ht="16.5" customHeight="1">
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+    </row>
+    <row r="28" spans="4:6" ht="16.5" customHeight="1"/>
+    <row r="29" spans="4:6" ht="16.5" customHeight="1"/>
+    <row r="30" spans="4:6" ht="16.5" customHeight="1"/>
+    <row r="31" spans="4:6" ht="16.5" customHeight="1"/>
+    <row r="32" spans="4:6" ht="16.5" customHeight="1"/>
     <row r="33" ht="16.5" customHeight="1"/>
     <row r="34" ht="16.5" customHeight="1"/>
     <row r="35" ht="16.5" customHeight="1"/>
@@ -1606,9 +1655,8 @@
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="B8:C8"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>